--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RskValBotDetailReport001.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RskValBotDetailReport001.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD153F14-0F71-4F71-A494-7D9A17EE476F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16635" windowHeight="3540"/>
   </bookViews>
   <sheets>
     <sheet name="穿透后底层明细表" sheetId="1" r:id="rId1"/>
@@ -15,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <r>
       <t>资产代码</t>
@@ -80,6 +79,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>穿透后底层资产持有价值（系统）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>G06科目</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -103,7 +106,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
@@ -257,7 +260,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -332,23 +335,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -384,23 +370,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -576,18 +545,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="5" width="24.75" style="2" customWidth="1"/>
     <col min="6" max="6" width="24.75" style="3" customWidth="1"/>
     <col min="7" max="13" width="24.75" style="4" customWidth="1"/>
-    <col min="14" max="18" width="24.75" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="1"/>
+    <col min="14" max="19" width="24.75" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="10" customFormat="1" ht="12.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:19" s="10" customFormat="1" ht="12.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -627,10 +596,10 @@
       <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="9" t="s">
@@ -641,6 +610,9 @@
       </c>
       <c r="R1" s="9" t="s">
         <v>17</v>
+      </c>
+      <c r="S1" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
